--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-diagnosen-codes.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-diagnosen-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T08:25:56+00:00</t>
+    <t>2026-09-14T07:00:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-diagnosen-codes.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-diagnosen-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:00:54+00:00</t>
+    <t>2026-09-14T09:05:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-diagnosen-codes.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-diagnosen-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T09:05:35+00:00</t>
+    <t>2026-09-14T11:50:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-diagnosen-codes.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-diagnosen-codes.xlsx
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>AtEDiagDiagnosenCodes</t>
+    <t>AtEDiagConditionCode</t>
   </si>
   <si>
     <t>Title</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T11:50:31+00:00</t>
+    <t>2026-09-15T06:30:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
